--- a/AAII_Financials/Quarterly/BORAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BORAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>BORAY</t>
   </si>
@@ -656,65 +656,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -745,8 +749,11 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -777,8 +784,11 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +819,11 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,8 +836,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -855,8 +869,11 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,8 +904,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -919,8 +939,11 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -951,8 +974,11 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,8 +988,9 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -994,8 +1021,11 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1026,8 +1056,11 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,8 +1073,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1072,8 +1106,11 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1104,8 +1141,11 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1136,8 +1176,11 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1168,8 +1211,11 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1200,8 +1246,11 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,8 +1281,11 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1264,8 +1316,11 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1296,8 +1351,11 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1386,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1421,11 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1456,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,8 +1491,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1456,8 +1526,11 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1488,8 +1561,11 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,8 +1596,11 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1552,45 +1631,51 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1688,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,40 +1703,44 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>265000</v>
+      </c>
+      <c r="E41" s="3">
         <v>151100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>161700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>144600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>147400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>154000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>177800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>196100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>169600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>252300</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1658,7 +1748,7 @@
         <v>1800</v>
       </c>
       <c r="E42" s="3">
-        <v>1900</v>
+        <v>1700</v>
       </c>
       <c r="F42" s="3">
         <v>1900</v>
@@ -1667,246 +1757,270 @@
         <v>1900</v>
       </c>
       <c r="H42" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I42" s="3">
         <v>1800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>63800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>331100</v>
+      </c>
+      <c r="E43" s="3">
         <v>311500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>305900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>294600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>289300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>325300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>343100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>353200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>328400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>129500</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>131500</v>
+      </c>
+      <c r="E44" s="3">
         <v>116000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>108600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>105600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>110300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>123300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>167900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>171200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>153400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>75700</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>14600</v>
+        <v>12300</v>
       </c>
       <c r="E45" s="3">
+        <v>14700</v>
+      </c>
+      <c r="F45" s="3">
         <v>16300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>29100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>40300</v>
       </c>
-      <c r="H45" s="3">
-        <v>54800</v>
-      </c>
       <c r="I45" s="3">
+        <v>35100</v>
+      </c>
+      <c r="J45" s="3">
         <v>3600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>766800</v>
+      </c>
+      <c r="E46" s="3">
         <v>619500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>615800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>599500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>608100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>659200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>713200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>750000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>749900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>495700</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>186100</v>
+        <v>175600</v>
       </c>
       <c r="E47" s="3">
+        <v>182800</v>
+      </c>
+      <c r="F47" s="3">
         <v>188800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>198300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>166900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>153900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>365100</v>
+      </c>
+      <c r="E48" s="3">
         <v>354800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>356100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>358800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>366700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>338800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>381600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>375400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>341800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>234300</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>265200</v>
+      </c>
+      <c r="E49" s="3">
         <v>194000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>198900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>204300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>212300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>195900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>230000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>181600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>180200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>172900</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2051,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,40 +2086,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>28200</v>
+        <v>29500</v>
       </c>
       <c r="E52" s="3">
+        <v>31500</v>
+      </c>
+      <c r="F52" s="3">
         <v>27100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17200</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2156,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1636900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1417500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1423900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1434900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1435000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1405300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1388300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1371900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1334500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>958900</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2208,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,200 +2223,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E57" s="3">
         <v>29300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>27000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>25700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>27800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>243600</v>
+      </c>
+      <c r="E58" s="3">
         <v>142700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>182200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>225400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>124700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>106900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>119100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>106900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>282100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>147600</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>276300</v>
+        <v>313200</v>
       </c>
       <c r="E59" s="3">
-        <v>209000</v>
+        <v>271900</v>
       </c>
       <c r="F59" s="3">
+        <v>208400</v>
+      </c>
+      <c r="G59" s="3">
         <v>202400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>261300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>326900</v>
       </c>
-      <c r="I59" s="3">
-        <v>273900</v>
-      </c>
       <c r="J59" s="3">
+        <v>270300</v>
+      </c>
+      <c r="K59" s="3">
         <v>214400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>280000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>219900</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>591500</v>
+      </c>
+      <c r="E60" s="3">
         <v>448300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>424200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>459400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>419700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>464100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>421200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>413200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>628000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>409200</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>442100</v>
+      </c>
+      <c r="E61" s="3">
         <v>406000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>398200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>416000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>482500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>432500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>459700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>483300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>290800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>135300</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10200</v>
+        <v>15800</v>
       </c>
       <c r="E62" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F62" s="3">
         <v>7600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2466,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2501,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2536,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1085700</v>
+      </c>
+      <c r="E66" s="3">
         <v>897500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>867500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>920200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>953900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>949800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>933100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>933200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>953300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>600600</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2588,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2621,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2656,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2691,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +2726,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>240500</v>
+      </c>
+      <c r="E72" s="3">
         <v>222000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>265800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>262900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>252400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>209500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>214200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>204700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>166300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>132300</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2796,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +2831,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +2866,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>475400</v>
+      </c>
+      <c r="E76" s="3">
         <v>455600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>489800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>447200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>410200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>393700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>389800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>372100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>294800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>271800</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,45 +2936,51 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2816,8 +3011,11 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,31 +3028,32 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E83" s="3">
         <v>5900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5500</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="3">
-        <v>3600</v>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I83" s="3">
         <v>3600</v>
       </c>
       <c r="J83" s="3">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="K83" s="3">
         <v>3300</v>
@@ -2862,8 +3061,11 @@
       <c r="L83" s="3">
         <v>3300</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3096,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3131,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3166,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3201,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3236,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E89" s="3">
         <v>19900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>39100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>18700</v>
       </c>
-      <c r="G89" s="3">
-        <v>46500</v>
-      </c>
       <c r="H89" s="3">
-        <v>40400</v>
+        <v>45800</v>
       </c>
       <c r="I89" s="3">
+        <v>41000</v>
+      </c>
+      <c r="J89" s="3">
         <v>-7400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>65500</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,40 +3288,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3600</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M91" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3356,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3391,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-46400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-42500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-39000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5500</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3">
         <v>-15000</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,40 +3443,44 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>47500</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>38800</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3511,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3546,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,100 +3581,112 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>141000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-17200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-19300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>19600</v>
       </c>
-      <c r="G100" s="3">
-        <v>-17200</v>
-      </c>
       <c r="H100" s="3">
-        <v>-26100</v>
+        <v>-16500</v>
       </c>
       <c r="I100" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="J100" s="3">
         <v>4000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-30600</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3">
         <v>128500</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="E101" s="3">
         <v>3500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6700</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3">
         <v>4600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-6100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>6000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>113100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>21300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-27900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>22600</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>156800</v>
       </c>
     </row>
